--- a/data/reports/FIXES_SINCE_HANDOVER_20261003.xlsx
+++ b/data/reports/FIXES_SINCE_HANDOVER_20261003.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2024,6 +2024,126 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>scheduler quarantine-terminal (mine)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>10-03 06:57</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>tools/v15_fleet_scheduler.py + tests/test_v15_quar_terminal.py</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>backup before_quarterm_202610030657; snapshot quarantined=107 live</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>deployed 1c96d52b fleet-wide; attempts reset 233 keys; 9 launches, 0 violations</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Probe reports verdict-IMPOSSIBLE; side_state terminal. Root cause of stall: 229 keys at cap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>s2 engine revert 06:28 + restore (mine)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>10-03 06:28/06:5x</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>s2 v12_quick_engine.py</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>s2 file mtime 06:28, 771475B = pre-selltop backup image</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>APPLIED</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>restored 98bd3e9e, holding; reverter unknown</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>NEVER-REVERT violation by unknown hand; logged + peers notified</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>herd stop attempt (mine)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>10-03 06:5x</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>s1/s2 herd daemons (PIDs 424203/514139 SIGTERM)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>ps verified dead, revived &lt;60s (PIDs 3343076/1183120); no cron/timer found</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>REVERTED-BY-OTHER</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>herds running latest 4e9c8210, claim+tombstone fenced</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Left running (~nil harm); needs user call to kill supervisor/peer intent</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2035,7 +2155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2465,6 +2585,36 @@
       <c r="F14" t="inlineStr">
         <is>
           <t>Superseded: fleet converged to LATEST per user order instead</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ablation-bolds crypto templates (peer, Mac 06:37)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>backups/before_ablation_bolds_20261003_*</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SPREADSHEETS/TEMPLATE_CRYPTO_{LONG,SHORT}.xlsx</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Bold True-&gt;False on ~25 ABLATION rows but is_default NOT flipped -&gt; DEFAULTS-GATE (bold!=YES) would refuse ALL pilots</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>HELD on Mac; peer must flip L to match + audit clean, then Mac-&gt;s1-&gt;fleet + NORM rebuild</t>
         </is>
       </c>
     </row>
@@ -2626,27 +2776,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0441ff42</t>
+          <t>1c96d52b</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0441ff42</t>
+          <t>1c96d52b</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0441ff42</t>
+          <t>1c96d52b</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0441ff42</t>
+          <t>1c96d52b</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>MATCH (S64 env still INGEST_BEST — see NOT_APPLIED #5)</t>
+          <t>MATCH (quarantine-terminal; S64 env still INGEST_BEST)</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3908,6 +4058,54 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Quarantine (07:00Z)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>107 sym_sides verdict-IMPOSSIBLE, now terminal (no relaunch, no burn)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Attempts reset (07:00Z)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>233 keys cleared (backup fleet_scheduler_state.before_quarterm_20261003.json); 07:02 tick launched 9, 0 violations</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Herds</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Running latest on s1/s2 despite stop attempt (revived &lt;60s, supervisor unknown); fenced, ~nil harm; user call pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Mac template drift</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Crypto TEMPLATE_* 06:37 ablation-bolds HELD (gate-breaking); fleet on gate-clean boolbold set</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/reports/FIXES_SINCE_HANDOVER_20261003.xlsx
+++ b/data/reports/FIXES_SINCE_HANDOVER_20261003.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2141,6 +2141,206 @@
       <c r="H42" t="inlineStr">
         <is>
           <t>Left running (~nil harm); needs user call to kill supervisor/peer intent</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>best-not-newest publish (mine, unlock v15_pilot.py)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>10-03 07:5x</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>v15_pilot.py publish block + _rank/_apply_best_publish; tests/test_v15_besteffort.py (22)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>backups/before_besteffort_202610030738_*; 22/22 pass; md5 a35d19f4 s1+s2</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>deployed s1+s2; one-time collapse: s1 268 restored/396 demoted, s2 236/110; median active gain 9.89-&gt;14.90; quarantine invariant re-guarded (89+67 redemoted)</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Qualified beats flagged regardless of gain; ties keep incumbent; losers history-filed, never deleted. s5 fenced, untouched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>NO_TRADES skip (mine, skip-dead-fills order)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>10-03 07:5x</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>v15_pilot.py below-floor block + SOFT-SKIP/SOFT-REFRESH gates (3 sites)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>22/22 pass incl stamp/hole tests; live on s1+s2</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>APPLIED</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0-trade + blockers-empty sheets: XLS kept, sweep skipped, no REDO; rerun only on newer NPZ</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Countermands 09-29/30 sweep-anyway. Below-floor-but-trading still sweeps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BEST_EFFORT near-miss publish (mine, best-effort order)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>10-03 07:5x</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>v15_pilot.py DONE stage + 365D gate + _nearmiss_30d</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>22/22 pass; live on s1+s2</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>APPLIED</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Valid near-miss (TIM/BH/content, 365D-valid-miss) publishes flagged, no quarantine, no REDO; vomit/invalid still quarantines</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>58/90 quarantined are near-miss class (data/reports/quarantine_classes_20261003.json) — retrospective flip proposed, NOT applied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>REDO cap (mine)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>10-03 07:5x</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>v15_pilot.py 3 REDO sites + _board_has_retryable_holes</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>22/22 pass</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>APPLIED</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>No REDO when repaired set has 0 trades or content-gate has zero retryable holes; RULE#3/365D-repair REDO kept</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Re-fill with identical overrides reproduces identical nulls — pure burn eliminated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>scheduler soft-terminal (mine)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>10-03 07:5x</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>tools/v15_fleet_scheduler.py HOST_PY probe regex + _VERDICT_TERMINAL_RE; tests/test_v15_quar_terminal.py updated</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>6/6 pass incl HOST_PY compile; md5 821e7fda s1+s2; ticks 07:44-48 launching, alert null</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>NO_TRADES/BEST_EFFORT join IMPOSSIBLE as terminal (no relaunch, no burn); next round re-evaluates</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>No herd edit needed (paced loop, fast-exits).</t>
         </is>
       </c>
     </row>
@@ -3931,7 +4131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4106,6 +4306,54 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Best-publish (07:50Z)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LIVE s1+s2 (pilot a35d19f4, sched 821e7fda); book median gain 9.89-&gt;14.90; 446 single-best actives (4 unparseable left, reported)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Dead-fill skip (07:50Z)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LIVE: 0-trade sheets skip sweep+REDO, rerun on NPZ refresh only</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Near-miss policy (07:50Z)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LIVE prospectively; 58 quarantined are near-miss class — retrospective BEST_EFFORT flip awaiting user call</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Pre-existing test failures</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>test_v15_pilot x2 (missing TEMPLATE.xlsx + absent string, proven in backup) + test_hao_finished_broken (Mac-local None deltas) — untouched, not mine</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/reports/FIXES_SINCE_HANDOVER_20261003.xlsx
+++ b/data/reports/FIXES_SINCE_HANDOVER_20261003.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2344,6 +2344,166 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>48</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>unsettled-none healer</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>10-03 09:1x</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>tools/v15_row_guards.py, tests/test_v15_row_guards.py</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>row_needs_recalc drops delta-None+empty-reason; dry-run NKE 858/GRAM 734 drops, BABA 0; pytest 19/19</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>35b228f7 uniform s1/s2/s5</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>heals 90k pre-fix identity/crash rows to 0.0-or-values on resume/REDO rebuild; settled verdicts stand</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>49</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>vec_unwired rescue TRADES_PER_SYM_PER_DAY_MAX</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>10-03 09:3x</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>data/vec_unwired.json 162-&gt;161</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>func-level vec read: overtrade_guard.blocked called from simulate_one L12828; 1622 rows affected</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>APPLIED</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>701fea2d uniform (then extended)</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>only ledger entry with eval-path read; 156 module-only + 5 no-hit confirmed dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>50</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>vec_unwired extend +23 never-movers</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>10-03 10:0x</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>data/vec_unwired.json 161-&gt;184</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>fleet-strict never (0 nonzero s1+s2+s5) + no func-level vec read + not rescued; 3 live-functional flagged as parity gaps</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>APPLIED</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>16ae46a2 uniform s1/s2/s5</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>BOTTOM_EXIT_HTF_WT_VETO/HTF_WT_CHURN/INTRADAY_RATIO_TRIM need engine unlock to test in vec</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>51</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>template greyfix: 127 deletes + 21 sets + FINAL_NORM regen</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>10-03 09:2x-09:4x</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SPREADSHEETS/TEMPLATE_*.xlsx x4 + TEMPLATE_FINAL_NORM x4</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>compat audit 145 fails -&gt; 0; norm unresolved 0/0/0/0; DELTA none-&gt;OFF (parity); LR_BAND dict rows untestable removed; 17 bool bolds restored to True</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>APPLIED</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>md5 uniform s1/s2/s5 (016d8eb1/f959d797/41fb1cf5/9a55b879)</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>kills TYPE_MISMATCH/override/INVENTED_ALT/NO_CANDIDATE rows on future boards; backups before_tpl_greyfix_*</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2355,7 +2515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2815,6 +2975,126 @@
       <c r="F15" t="inlineStr">
         <is>
           <t>HELD on Mac; peer must flip L to match + audit clean, then Mac-&gt;s1-&gt;fleet + NORM rebuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>16</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SHORT WT_DC veto flip</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>10-03 09:0x</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SPREADSHEETS/TEMPLATE_CRYPTO_SHORT.xlsx (no change)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>14 WT_DC_SHORT_ENABLED=True rows all delta 0.0 with 54-317 trades; ez ignores switch; bold already True in effect</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CLOSED-FALSE-ALARM</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>no veto active; crypto SHORT boards trade normally</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>V15_ADAPT_BASELINE flip to 1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>10-03 09:2x</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>tools/v15_fleet_scheduler.py:362, tools/v15_local_herd.py:866 (no change)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>BABA_SHORT 1656 floor-rows are honest quiet-window outcomes; ADAPT=1 would violate §64 defaults-pure</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ZERO_TRADES/floor rows keep honest 0.0 + reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>18</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>DELTA_HTF_GATE none pilot-parse change</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>10-03 09:3x</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>v15_pilot.py:2618 (no change)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vec applies phantom 15m veto for non-TF values (live skips via _B1_REAL_TFS); 'OFF' is parity-correct in both</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SUPERSEDED</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>fixed in template instead (none-&gt;OFF x3); vec/live gap on hh_hl_4h/4h_D stays engine backlog</t>
         </is>
       </c>
     </row>

--- a/data/reports/FIXES_SINCE_HANDOVER_20261003.xlsx
+++ b/data/reports/FIXES_SINCE_HANDOVER_20261003.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2501,6 +2501,46 @@
       <c r="H51" t="inlineStr">
         <is>
           <t>kills TYPE_MISMATCH/override/INVENTED_ALT/NO_CANDIDATE rows on future boards; backups before_tpl_greyfix_*</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>52</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>v15_switch_healer daemon (s1)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>10-03 22:25</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>tools/v15_switch_healer.py NEW, tests/test_v15_switch_healer.py, s1 @reboot cron</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>dry-runs Mac+s1 clean (peer guard excluded 2+2 movers); 7/7 tests; pid 2087321 live, interval 30m, budget 25/40</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>APPLIED</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>s1-only daemon (code synced fleet-wide d2cb25e7)</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>audits wiring/live-pos_sym/template each cycle; fixes ledger+templates, journals all, engine gaps to backlog; flock singleton</t>
         </is>
       </c>
     </row>

--- a/data/reports/FIXES_SINCE_HANDOVER_20261003.xlsx
+++ b/data/reports/FIXES_SINCE_HANDOVER_20261003.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2544,6 +2544,300 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>C2-1</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>cut2 v12 lane-C twins: 21 hunks + batch1/exhaust/mtf-bypass inserts</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>v12_quick_engine.py</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>s1 gate cut2==drift bitwise (MU 1.4050855278619192/111/0.72029/0.01729 16dp); py_compile</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>s1/s2/s5 sb+live 17/17 md5 ec615c57</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>10 flips live-verified; WT_DIV twin skipped (choke covers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>C2-2</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>cut2 obligatory_reentry_vec 4-tuple + score</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>vec_decisions/obligatory_reentry_vec.py</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>sole-caller proof (v12:12716 only); LEGACY smoke MU 1.405-&gt;1.736 +1 trade</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>s1/s2/s5 sb+live 9b505132</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>v12 call site updated same cut; try/except armor both dirs</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>C2-3</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>cut2 ez/tradier/config/tconfig mop mirrors (11 hunks)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ez_manage.py tradier_manage.py config.py config_tradier.py</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>11/11 hunks 100% +lines verbatim in parent (52/52,27/27,29/29,...)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>s1/s2/s5 sb+live md5</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>ENTRY_DC+KZONE/SHORTx5/OBLIG/SIMPLE_TP/BB; K_ZONE_MIRROR+BB_SQUEEZE fields</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>C2-4</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>cut2 11 wire modules (wirec x8 + wirem x3)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>vec_decisions/wirec_*.py wirem_*.py</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>md5 SAME as laneM staged; 21 twin fns exist; inert-at-default read-verified</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>s1/s2/s5 added (were absent)</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>execnow_guards/sizing/wt_gates/entry_tf fully read; rest gate-covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>C2-5</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>cut2 restore SFK + ported_entry (own cut2-cp regression)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>vec_decisions/process_position_crypto__stop_functions_kill.py ported_entry.py</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Sept-fix markers 2; staged GR blocks 1; md5 == fleet (2a8eb5cb/9c80691b)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>already uniform, no deploy</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>stale worktree copies (05-30/10-02) had clobbered parent 02:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>C2-6</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>cut2 drift preserved 100% (no reversions)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>all 5 engines</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>M contains X adds 32/32; 28 stale hunks skipped; parent-newer ALL-15M kept over fleet</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>fleet upgraded (ORCL restored s2/s5)</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>parity-cut BASE_TF/HTF/LIVE_ENTRY/MTF/LH_LL/TARGET-DC intact</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>C2-7</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>cut2 full-tree gate (production evaluate_sanitized)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>tools path</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>s1 /tmp/gate_out_{drift,cut2,band,smoke*}.jsonl; real==staged BTC 0/0.0/2881</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>gate only</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>5-sym panel; cut2+band==drift; DD/BTC smoke no-crash (no entries to fire)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2555,7 +2849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3137,6 +3431,244 @@
           <t>fixed in template instead (none-&gt;OFF x3); vec/live gap on hh_hl_4h/4h_D stays engine backlog</t>
         </is>
       </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>C2-S1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>laneM v12 seed-artifact reversions (28 hunks)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>laneM patch 02:36</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>v12</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>stale pre-drift seed; would revert live-parity fixes (BASE_TF/HTF/MTF-zeroing)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NEVER APPLY; drift is newer+verified</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>C2-S2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>laneM ported_entry 68-line strip</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>laneM patch 02:36</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ported_entry.py</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>worktree seed 10-02 predates staged ENTRY_VET/STDEV/WT_DIV/LR_BAND/GR twins</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NEVER APPLY; parent==fleet rich version kept</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>C2-S3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>laneM SFK module revert</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>laneM patch 02:36</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>stop_functions_kill.py</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>worktree seed 05-30 predates 2026-09-28 kill-gate leak fix (57 leaks/24h)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>NEVER APPLY; Sept fix kept</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>C2-S4</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>laneM WT_DIV lane-C twin line</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>laneM patch h27</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>v12</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>redundant: staged _ec_choke_block covers WT_DIV at live-True; twin unverified-firing</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SKIP (exhaust twin applied); revisit if choke removed</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>C2-S5</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>laneM WT_EXHAUST divergence comment</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>laneM patch h23</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>v12</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>FALSE claim: live WT_EXHAUST=False both venues (not True); no divergence exists</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SKIP comment; twin applied (inert at False)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>C2-S6</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>laneM config ENTRY_DC field MOVE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>laneM patch</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>config.py config_tradier.py</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>same name+default, new location only; zero semantic effect</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SKIP move; fixed stale Live-twin-pending comment instead</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>C2-S7</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>crypto entry flatline fix (0 trades majors+alts)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>gate finding</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>v12 entry pipeline</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>root cause unisolated: WT_DIV-off still 0; ENTRY_SCORE_THRESHOLD=0 still 0; staged choke cleared (all legs permissive)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>DEDICATED DEBUG WORKSTREAM NEXT (stage instrumentation)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/reports/FIXES_SINCE_HANDOVER_20261003.xlsx
+++ b/data/reports/FIXES_SINCE_HANDOVER_20261003.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2835,6 +2835,245 @@
       <c r="H59" t="inlineStr">
         <is>
           <t>5-sym panel; cut2+band==drift; DD/BTC smoke no-crash (no entries to fire)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>C5-1</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>cut5 unify: parent(16h lanes) + fleet cut#4 reconciled, L1 triaged, TVS RSI/H3 removed</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>5 engines + twin_vec_special/orange_ports/reentry_staged</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>dual-gen gate s1+s2 (BTC 216/-2.86, SHORT 194, ETH 156, MU 59/1.35); test 3/3</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>s1/s2/s5 sb+live 8/8 c678cf6d</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>s1-only 15+3 older-direct, zero ports (TYF wins)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>C5-2</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>cut5 TVS RSI-AND removed (zeroed BTC/ETH/MU) + H3 DELTA removed (no live side)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>v12_quick_engine.py</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>bisect: cut4-v12 restores 145; live RSI touches-only; wt_dc_delta.py absent</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>same cut</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>DC-OR/R3/churn/ebrake kept (live real); comment cites fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>C5-3</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>NPZ generations reunified (s2/s5 resynced to s1 dfd5a871 during day)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>backtest_v8/indicators/*.npz</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>s1=s2=s5 dfd5a871 BTC; s2-cut4 == s1-cut4 bitwise</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>OBSERVED</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>fleet data</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>V1 256t explained (stale s2-gen); same-host rule stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>L2-R3</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Live mirrors N-Z: 58 already-wired by peers, 4 honest-0 (L2-R3)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>/tmp/laneL2r3_out/proofs.jsonl</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>3/3 parent spot-check PASS (B16/QUICK_REDUCE/CHURN)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>APPLIED</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>0-byte patch; bounce x3 deferred to V2-R3 family verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>V2-R3</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Vec twins N-Z: 9 wired_skip (5 MOVED firing-proven, 4 HONEST0), 32 blocked grounded</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>/tmp/laneV2r3_out/proofs.jsonl</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2/2 parent spot-check PASS (TRADIER_DC MOVED, WT_COMPOSITE blocked)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>APPLIED</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>0-byte patch; s5 staged firing BTC/ETH/AAPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>BOUNCE-FAM</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BOUNCE_REENTRY family verdict: unsuffixed ENABLED=VEC-ONLY, K_RESETx2=PHANTOM-VEC+HONEST0-live, _TRADIERx3=LIVE-ONLY</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ez_manage.py:6785 kill,6914 unreachable; v12:360 func,366 no-op; tradier:23030 real</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>parent-verified: user 2026-10-01 _batch1 kill stands; vec (_c&gt;0) no-op confirmed</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>APPLIED</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>no code change by design; never promote unsuffixed; do not fix phantom (live user-killed)</t>
         </is>
       </c>
     </row>
@@ -3463,8 +3702,6 @@
           <t>NEVER APPLY; drift is newer+verified</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3497,8 +3734,6 @@
           <t>NEVER APPLY; parent==fleet rich version kept</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3531,8 +3766,6 @@
           <t>NEVER APPLY; Sept fix kept</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3565,8 +3798,6 @@
           <t>SKIP (exhaust twin applied); revisit if choke removed</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3599,8 +3830,6 @@
           <t>SKIP comment; twin applied (inert at False)</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3633,8 +3862,6 @@
           <t>SKIP move; fixed stale Live-twin-pending comment instead</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3667,8 +3894,6 @@
           <t>DEDICATED DEBUG WORKSTREAM NEXT (stage instrumentation)</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
